--- a/data/trans_orig/P1404-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1404-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2007</t>
+          <t>Población con diagnóstico de colesterol alto en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7754</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485419</t>
+          <t>485442</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>493133</t>
+          <t>493138</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>459735</t>
+          <t>461721</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>949850</t>
+          <t>950864</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>959726</t>
+          <t>959771</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>11183</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>19726</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>25719</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>723918</t>
+          <t>724306</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>733644</t>
+          <t>733638</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>605696</t>
+          <t>605768</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>619712</t>
+          <t>619727</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1336141</t>
+          <t>1335263</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1351909</t>
+          <t>1351971</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18842</t>
+          <t>18852</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39759</t>
+          <t>40520</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17200</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37090</t>
+          <t>36602</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38939</t>
+          <t>39073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68383</t>
+          <t>67276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>598909</t>
+          <t>598148</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>619826</t>
+          <t>619816</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>652654</t>
+          <t>653142</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>672544</t>
+          <t>673051</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1260029</t>
+          <t>1261136</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1289473</t>
+          <t>1289339</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40391</t>
+          <t>41142</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66892</t>
+          <t>68425</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31707</t>
+          <t>31944</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56505</t>
+          <t>55680</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79661</t>
+          <t>77898</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116623</t>
+          <t>115898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>452255</t>
+          <t>450722</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>478756</t>
+          <t>478005</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>459137</t>
+          <t>459962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>483935</t>
+          <t>483698</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>918166</t>
+          <t>918891</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>955128</t>
+          <t>956891</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55001</t>
+          <t>55222</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82650</t>
+          <t>84197</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69759</t>
+          <t>70590</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101161</t>
+          <t>104163</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>135331</t>
+          <t>133176</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>176203</t>
+          <t>175631</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>304060</t>
+          <t>302513</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>331709</t>
+          <t>331488</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>302825</t>
+          <t>299823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>334227</t>
+          <t>333396</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>614493</t>
+          <t>615065</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>655365</t>
+          <t>657520</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44654</t>
+          <t>45818</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70128</t>
+          <t>72490</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>81591</t>
+          <t>80749</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112317</t>
+          <t>112749</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>134590</t>
+          <t>132427</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>177484</t>
+          <t>174425</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,45%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222455</t>
+          <t>220093</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247929</t>
+          <t>246765</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>230617</t>
+          <t>230185</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>261343</t>
+          <t>262185</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>458033</t>
+          <t>461092</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>500927</t>
+          <t>503090</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>79,16%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33919</t>
+          <t>33622</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>56774</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69980</t>
+          <t>69635</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>103631</t>
+          <t>104260</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111976</t>
+          <t>111143</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>152436</t>
+          <t>150755</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>153452</t>
+          <t>153109</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175964</t>
+          <t>176261</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>229648</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>263928</t>
+          <t>264273</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>391355</t>
+          <t>393036</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>431815</t>
+          <t>432648</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,56%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>231228</t>
+          <t>229997</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>294029</t>
+          <t>291763</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>314712</t>
+          <t>312640</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>383461</t>
+          <t>385338</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>561745</t>
+          <t>561635</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>655564</t>
+          <t>658087</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2982514</t>
+          <t>2984780</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3045315</t>
+          <t>3046546</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2995736</t>
+          <t>2993859</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3064485</t>
+          <t>3066557</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6000177</t>
+          <t>5997654</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6093996</t>
+          <t>6094106</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2012</t>
+          <t>Población con diagnóstico de colesterol alto en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,97 +3712,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6273</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1934</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6648</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6636</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1934</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6864</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>423582</t>
+          <t>423957</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>877512</t>
+          <t>877740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25884</t>
+          <t>27625</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16422</t>
+          <t>16502</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14570</t>
+          <t>14585</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35503</t>
+          <t>35273</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>661203</t>
+          <t>659462</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>678766</t>
+          <t>677915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>593833</t>
+          <t>593753</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>607081</t>
+          <t>607170</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1261839</t>
+          <t>1262069</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1282772</t>
+          <t>1282757</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28855</t>
+          <t>29004</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54274</t>
+          <t>54543</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19233</t>
+          <t>18616</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40208</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51861</t>
+          <t>53097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85713</t>
+          <t>84366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>627589</t>
+          <t>627320</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>653008</t>
+          <t>652859</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>669366</t>
+          <t>670562</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>690341</t>
+          <t>690958</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1305724</t>
+          <t>1307071</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1339576</t>
+          <t>1338340</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42278</t>
+          <t>43123</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72190</t>
+          <t>74170</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60416</t>
+          <t>60216</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93534</t>
+          <t>96339</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108483</t>
+          <t>110894</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157240</t>
+          <t>155840</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>541018</t>
+          <t>539038</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>570930</t>
+          <t>570085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>520730</t>
+          <t>517925</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>553848</t>
+          <t>554048</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1070232</t>
+          <t>1071632</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1118989</t>
+          <t>1116578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,97%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66274</t>
+          <t>67373</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100569</t>
+          <t>100848</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98653</t>
+          <t>97643</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>139295</t>
+          <t>135455</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>175918</t>
+          <t>173346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228813</t>
+          <t>224210</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>328860</t>
+          <t>328581</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>363155</t>
+          <t>362056</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>308505</t>
+          <t>312345</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>349147</t>
+          <t>350157</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>648416</t>
+          <t>653019</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>701311</t>
+          <t>703883</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,24%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94724</t>
+          <t>95605</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>130506</t>
+          <t>130901</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>106938</t>
+          <t>105876</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>143720</t>
+          <t>140779</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>213026</t>
+          <t>212063</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>264282</t>
+          <t>265665</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,02%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179280</t>
+          <t>178885</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>215062</t>
+          <t>214181</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>210276</t>
+          <t>213217</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247058</t>
+          <t>248120</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>399500</t>
+          <t>398117</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>450756</t>
+          <t>451719</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66216</t>
+          <t>66621</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97329</t>
+          <t>100356</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>118988</t>
+          <t>118614</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>157876</t>
+          <t>158760</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>193700</t>
+          <t>194358</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>243824</t>
+          <t>241238</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>152522</t>
+          <t>149495</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>183635</t>
+          <t>183230</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>231103</t>
+          <t>230219</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>269991</t>
+          <t>270365</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>395006</t>
+          <t>397592</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>445130</t>
+          <t>444472</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,58%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>350005</t>
+          <t>349516</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>433817</t>
+          <t>429276</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>451920</t>
+          <t>448403</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>534745</t>
+          <t>533428</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>825046</t>
+          <t>822841</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>935506</t>
+          <t>934543</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2991553</t>
+          <t>2996094</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3075365</t>
+          <t>3075854</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3020353</t>
+          <t>3021670</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3103178</t>
+          <t>3106695</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6044963</t>
+          <t>6045926</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6155423</t>
+          <t>6157628</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,21%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2016</t>
+          <t>Población con diagnóstico de colesterol alto en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413401</t>
+          <t>413570</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390142</t>
+          <t>390804</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>808476</t>
+          <t>808453</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>23041</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16088</t>
+          <t>16253</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13433</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33261</t>
+          <t>33310</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>569126</t>
+          <t>567455</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>584507</t>
+          <t>583634</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>547456</t>
+          <t>547291</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>558893</t>
+          <t>559656</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1120779</t>
+          <t>1120730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1140607</t>
+          <t>1140470</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20475</t>
+          <t>20425</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44406</t>
+          <t>44863</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27767</t>
+          <t>27075</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35759</t>
+          <t>35756</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63194</t>
+          <t>63339</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624691</t>
+          <t>624234</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>648622</t>
+          <t>648672</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>633619</t>
+          <t>634311</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>650283</t>
+          <t>650901</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1267289</t>
+          <t>1267144</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1294724</t>
+          <t>1294727</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50761</t>
+          <t>49961</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82698</t>
+          <t>82046</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54247</t>
+          <t>54989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85954</t>
+          <t>85678</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113289</t>
+          <t>111687</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155744</t>
+          <t>156272</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>563350</t>
+          <t>564002</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>595287</t>
+          <t>596087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>563123</t>
+          <t>563399</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>594830</t>
+          <t>594088</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1139381</t>
+          <t>1138853</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1181836</t>
+          <t>1183438</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78888</t>
+          <t>79150</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>113390</t>
+          <t>116054</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>101446</t>
+          <t>98889</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>141294</t>
+          <t>142215</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>187685</t>
+          <t>188271</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>242036</t>
+          <t>241147</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>364528</t>
+          <t>361864</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>399030</t>
+          <t>398768</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>355555</t>
+          <t>354634</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>395403</t>
+          <t>397960</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>732731</t>
+          <t>733620</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>787082</t>
+          <t>786496</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,69%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90269</t>
+          <t>88157</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123833</t>
+          <t>121549</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>98790</t>
+          <t>100252</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>135110</t>
+          <t>137838</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>198411</t>
+          <t>200250</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>251346</t>
+          <t>249791</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>210497</t>
+          <t>212781</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>244061</t>
+          <t>246173</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>242652</t>
+          <t>239924</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>278972</t>
+          <t>277510</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>460746</t>
+          <t>462301</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>513681</t>
+          <t>511842</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,88%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67655</t>
+          <t>67258</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92679</t>
+          <t>94251</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>115252</t>
+          <t>114459</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>159541</t>
+          <t>157074</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>191902</t>
+          <t>192996</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>243613</t>
+          <t>241408</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,73%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>164319</t>
+          <t>162747</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>189343</t>
+          <t>189740</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>240628</t>
+          <t>243095</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>284917</t>
+          <t>285710</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>413554</t>
+          <t>415759</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>465265</t>
+          <t>464171</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,63%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>353120</t>
+          <t>353501</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>427140</t>
+          <t>427026</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>428174</t>
+          <t>428803</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>512181</t>
+          <t>514035</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>803469</t>
+          <t>802335</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>919823</t>
+          <t>915480</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2967210</t>
+          <t>2967324</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3041230</t>
+          <t>3040849</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3032361</t>
+          <t>3030507</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3116368</t>
+          <t>3115739</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6019069</t>
+          <t>6023412</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6135423</t>
+          <t>6136557</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2023</t>
+          <t>Población con diagnóstico de colesterol alto en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14899</t>
+          <t>14014</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15572</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298301</t>
+          <t>299186</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312095</t>
+          <t>312154</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>697615</t>
+          <t>697716</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>712109</t>
+          <t>712083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13681</t>
+          <t>13366</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19218</t>
+          <t>19498</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>8812</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26573</t>
+          <t>26685</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>409866</t>
+          <t>410181</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422144</t>
+          <t>422014</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>492286</t>
+          <t>492006</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506615</t>
+          <t>506496</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>908478</t>
+          <t>908366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>926048</t>
+          <t>926239</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17159</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38419</t>
+          <t>38588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11685</t>
+          <t>11952</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22750</t>
+          <t>23492</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46978</t>
+          <t>46770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>495513</t>
+          <t>495344</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>516773</t>
+          <t>516211</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530114</t>
+          <t>529847</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>537870</t>
+          <t>537970</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1028753</t>
+          <t>1028961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1052981</t>
+          <t>1052239</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37830</t>
+          <t>38838</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129266</t>
+          <t>129383</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59615</t>
+          <t>58013</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93203</t>
+          <t>91628</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96505</t>
+          <t>93922</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>201158</t>
+          <t>198638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>758520</t>
+          <t>758403</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>849956</t>
+          <t>848948</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>618491</t>
+          <t>620066</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>652079</t>
+          <t>653681</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1398322</t>
+          <t>1400842</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1502975</t>
+          <t>1505558</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115966</t>
+          <t>115947</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>153478</t>
+          <t>154149</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121803</t>
+          <t>121247</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150807</t>
+          <t>150244</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>246806</t>
+          <t>245491</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>294773</t>
+          <t>292938</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>405797</t>
+          <t>405126</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>443309</t>
+          <t>443328</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>393302</t>
+          <t>393865</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>422306</t>
+          <t>422862</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>808611</t>
+          <t>810446</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>856578</t>
+          <t>857893</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,75%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97108</t>
+          <t>96048</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124392</t>
+          <t>124447</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>208217</t>
+          <t>207137</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>501740</t>
+          <t>503280</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>312698</t>
+          <t>313267</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>701127</t>
+          <t>706859</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>240965</t>
+          <t>240910</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268249</t>
+          <t>269309</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>105489</t>
+          <t>103949</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>399012</t>
+          <t>400092</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>271459</t>
+          <t>265727</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>659888</t>
+          <t>659319</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,79%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91324</t>
+          <t>90492</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>115934</t>
+          <t>116205</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164320</t>
+          <t>165001</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>192407</t>
+          <t>191492</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>261611</t>
+          <t>261821</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>298814</t>
+          <t>300811</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>165961</t>
+          <t>165690</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>190571</t>
+          <t>191403</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>230914</t>
+          <t>231829</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>259001</t>
+          <t>258320</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>406401</t>
+          <t>404404</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>443604</t>
+          <t>443394</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>363541</t>
+          <t>365988</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>518525</t>
+          <t>515380</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>570321</t>
+          <t>572572</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1395833</t>
+          <t>1282956</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1017635</t>
+          <t>1019748</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1838309</t>
+          <t>1924356</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2933255</t>
+          <t>2936400</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3088239</t>
+          <t>3085792</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2257022</t>
+          <t>2369899</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3082534</t>
+          <t>3080283</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5266326</t>
+          <t>5180279</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6087000</t>
+          <t>6084887</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1404-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1404-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>855</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10689</t>
+          <t>11376</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485442</t>
+          <t>485192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>493138</t>
+          <t>493209</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>461721</t>
+          <t>461083</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>950864</t>
+          <t>950177</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>959771</t>
+          <t>959558</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11183</t>
+          <t>10712</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>18106</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9011</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25719</t>
+          <t>24187</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>724306</t>
+          <t>724777</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>733638</t>
+          <t>733615</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>605768</t>
+          <t>607388</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>619727</t>
+          <t>620331</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1335263</t>
+          <t>1336795</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1351971</t>
+          <t>1351962</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18852</t>
+          <t>18040</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40520</t>
+          <t>39557</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16693</t>
+          <t>15813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36602</t>
+          <t>36926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39073</t>
+          <t>40317</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67276</t>
+          <t>70121</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>598148</t>
+          <t>599111</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>619816</t>
+          <t>620628</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>653142</t>
+          <t>652818</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>673051</t>
+          <t>673931</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1261136</t>
+          <t>1258291</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1289339</t>
+          <t>1288095</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41142</t>
+          <t>40001</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68425</t>
+          <t>69096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31944</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55680</t>
+          <t>54230</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77898</t>
+          <t>78082</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115898</t>
+          <t>116673</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>450722</t>
+          <t>450051</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>478005</t>
+          <t>479146</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>459962</t>
+          <t>461412</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>483698</t>
+          <t>484541</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>918891</t>
+          <t>918116</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>956891</t>
+          <t>956707</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55222</t>
+          <t>54314</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84197</t>
+          <t>85754</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70590</t>
+          <t>67937</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104163</t>
+          <t>101232</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133176</t>
+          <t>134198</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175631</t>
+          <t>179157</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>302513</t>
+          <t>300956</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>331488</t>
+          <t>332396</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>299823</t>
+          <t>302754</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>333396</t>
+          <t>336049</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>615065</t>
+          <t>611539</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>657520</t>
+          <t>656498</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,03%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45818</t>
+          <t>45042</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72490</t>
+          <t>70694</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80749</t>
+          <t>80959</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112749</t>
+          <t>113566</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>132427</t>
+          <t>135074</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>174425</t>
+          <t>173504</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>220093</t>
+          <t>221889</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246765</t>
+          <t>247541</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>230185</t>
+          <t>229368</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>262185</t>
+          <t>261975</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>461092</t>
+          <t>462013</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>503090</t>
+          <t>500443</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>78,75%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33622</t>
+          <t>32928</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56774</t>
+          <t>56705</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69635</t>
+          <t>70465</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>104260</t>
+          <t>105180</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111143</t>
+          <t>112496</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>150755</t>
+          <t>152966</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>153109</t>
+          <t>153178</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>176261</t>
+          <t>176955</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>229648</t>
+          <t>228728</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>264273</t>
+          <t>263443</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>393036</t>
+          <t>390825</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>432648</t>
+          <t>431295</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,31%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>229997</t>
+          <t>227814</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>291763</t>
+          <t>290827</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>312640</t>
+          <t>312230</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>385338</t>
+          <t>383320</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>561635</t>
+          <t>562402</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>658087</t>
+          <t>654366</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2984780</t>
+          <t>2985716</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3046546</t>
+          <t>3048729</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2993859</t>
+          <t>2995877</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3066557</t>
+          <t>3066967</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5997654</t>
+          <t>6001375</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6094106</t>
+          <t>6093339</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>423957</t>
+          <t>424386</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>877740</t>
+          <t>876686</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27625</t>
+          <t>26198</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>17159</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14585</t>
+          <t>15303</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35273</t>
+          <t>37198</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>659462</t>
+          <t>660889</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>677915</t>
+          <t>678277</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>593753</t>
+          <t>593096</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>607170</t>
+          <t>606616</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1262069</t>
+          <t>1260144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1282757</t>
+          <t>1282039</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29004</t>
+          <t>27645</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54543</t>
+          <t>55186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>18252</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>38679</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53097</t>
+          <t>53094</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84366</t>
+          <t>86279</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>627320</t>
+          <t>626677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>652859</t>
+          <t>654218</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>670562</t>
+          <t>670895</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>690958</t>
+          <t>691322</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1307071</t>
+          <t>1305158</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1338340</t>
+          <t>1338343</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43123</t>
+          <t>41952</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74170</t>
+          <t>71286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60216</t>
+          <t>60092</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96339</t>
+          <t>94166</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110894</t>
+          <t>110888</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155840</t>
+          <t>155756</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>539038</t>
+          <t>541922</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>570085</t>
+          <t>571256</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>517925</t>
+          <t>520098</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>554048</t>
+          <t>554172</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1071632</t>
+          <t>1071716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1116578</t>
+          <t>1116584</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67373</t>
+          <t>67594</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100848</t>
+          <t>102144</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>97643</t>
+          <t>96379</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135455</t>
+          <t>135386</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>173346</t>
+          <t>173638</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>224210</t>
+          <t>224916</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>328581</t>
+          <t>327285</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>362056</t>
+          <t>361835</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>312345</t>
+          <t>312414</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>350157</t>
+          <t>351421</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>653019</t>
+          <t>652313</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>703883</t>
+          <t>703591</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,21%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95605</t>
+          <t>95420</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>130901</t>
+          <t>131733</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>105876</t>
+          <t>105399</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>140779</t>
+          <t>142913</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>212063</t>
+          <t>210061</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>265665</t>
+          <t>262523</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,55%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>178885</t>
+          <t>178053</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>214181</t>
+          <t>214366</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>213217</t>
+          <t>211083</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>248120</t>
+          <t>248597</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>398117</t>
+          <t>401259</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>451719</t>
+          <t>453721</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,35%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66621</t>
+          <t>66511</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>100356</t>
+          <t>98782</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>118614</t>
+          <t>118643</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>158760</t>
+          <t>156449</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,47 +5820,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>30,5%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>40,22%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>218766</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>194771</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>246045</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>34,24%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>30,49%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>40,81%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>218766</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>194358</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>241238</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>34,24%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>30,42%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>149495</t>
+          <t>151069</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>183230</t>
+          <t>183340</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>230219</t>
+          <t>232530</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>270365</t>
+          <t>270336</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,47 +5933,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>69,5%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>420064</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>392785</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>444059</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>65,76%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>61,49%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>69,51%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>420064</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>397592</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>444472</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>65,76%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>62,24%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>69,58%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>349516</t>
+          <t>351376</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>429276</t>
+          <t>433553</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>448403</t>
+          <t>446382</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>533428</t>
+          <t>532027</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>822841</t>
+          <t>821373</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>934543</t>
+          <t>935342</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2996094</t>
+          <t>2991817</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3075854</t>
+          <t>3073994</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3021670</t>
+          <t>3023071</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3106695</t>
+          <t>3108716</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6045926</t>
+          <t>6045127</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6157628</t>
+          <t>6159096</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5254</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>7555</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413570</t>
+          <t>414209</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390804</t>
+          <t>391278</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>808453</t>
+          <t>807663</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23041</t>
+          <t>22085</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16253</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33310</t>
+          <t>32996</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>567455</t>
+          <t>568411</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>583634</t>
+          <t>584077</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>547291</t>
+          <t>548018</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>559656</t>
+          <t>558927</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1120730</t>
+          <t>1121044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1140470</t>
+          <t>1140340</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20425</t>
+          <t>20155</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44863</t>
+          <t>43345</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27075</t>
+          <t>26739</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35756</t>
+          <t>37030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63339</t>
+          <t>66135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624234</t>
+          <t>625752</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>648672</t>
+          <t>648942</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>634311</t>
+          <t>634647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>650901</t>
+          <t>650075</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1267144</t>
+          <t>1264348</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1294727</t>
+          <t>1293453</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49961</t>
+          <t>51765</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82046</t>
+          <t>81698</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54989</t>
+          <t>55186</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85678</t>
+          <t>86010</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111687</t>
+          <t>113997</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>156272</t>
+          <t>157548</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>564002</t>
+          <t>564350</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>596087</t>
+          <t>594283</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>563399</t>
+          <t>563067</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>594088</t>
+          <t>593891</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1138853</t>
+          <t>1137577</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1183438</t>
+          <t>1181128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>79150</t>
+          <t>77658</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>116054</t>
+          <t>115797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98889</t>
+          <t>100261</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142215</t>
+          <t>139483</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>188271</t>
+          <t>184810</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>241147</t>
+          <t>240320</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>361864</t>
+          <t>362121</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>398768</t>
+          <t>400260</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>354634</t>
+          <t>357366</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>397960</t>
+          <t>396588</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>733620</t>
+          <t>734447</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>786496</t>
+          <t>789957</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>81,04%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88157</t>
+          <t>89470</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>121549</t>
+          <t>122459</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>100252</t>
+          <t>99479</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>137838</t>
+          <t>135524</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>200250</t>
+          <t>199671</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>249791</t>
+          <t>247526</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,76%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212781</t>
+          <t>211871</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246173</t>
+          <t>244860</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>239924</t>
+          <t>242238</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277510</t>
+          <t>278283</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>462301</t>
+          <t>464566</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>511842</t>
+          <t>512421</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,96%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67258</t>
+          <t>67898</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94251</t>
+          <t>93517</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>114459</t>
+          <t>115690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>157074</t>
+          <t>159530</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>192996</t>
+          <t>190994</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>241408</t>
+          <t>241323</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>162747</t>
+          <t>163481</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>189740</t>
+          <t>189100</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>243095</t>
+          <t>240639</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>285710</t>
+          <t>284479</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>415759</t>
+          <t>415844</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>464171</t>
+          <t>466173</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,94%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>353501</t>
+          <t>353223</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>427026</t>
+          <t>424568</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>428803</t>
+          <t>427646</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>514035</t>
+          <t>514429</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>802335</t>
+          <t>796559</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>915480</t>
+          <t>914997</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2967324</t>
+          <t>2969782</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3040849</t>
+          <t>3041127</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3030507</t>
+          <t>3030113</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3115739</t>
+          <t>3116896</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6023412</t>
+          <t>6023895</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6136557</t>
+          <t>6142333</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,52%</t>
         </is>
       </c>
     </row>
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14014</t>
+          <t>15546</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15471</t>
+          <t>14834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>308265</t>
+          <t>357151</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>299186</t>
+          <t>346966</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312154</t>
+          <t>361406</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>708252</t>
+          <t>764944</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>697716</t>
+          <t>755471</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>712083</t>
+          <t>769195</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13366</t>
+          <t>14721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10563</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19498</t>
+          <t>18945</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15862</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26685</t>
+          <t>27353</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>418205</t>
+          <t>470959</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410181</t>
+          <t>462169</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422014</t>
+          <t>475512</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>500984</t>
+          <t>490520</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>492006</t>
+          <t>482138</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506496</t>
+          <t>495638</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>919189</t>
+          <t>961479</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>908366</t>
+          <t>950620</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>926239</t>
+          <t>968647</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>31453</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>20941</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38588</t>
+          <t>44750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>18301</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>42812</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>30990</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46770</t>
+          <t>57646</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>507272</t>
+          <t>586849</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>495344</t>
+          <t>573552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>516211</t>
+          <t>597361</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>534893</t>
+          <t>610128</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>529847</t>
+          <t>603187</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>537970</t>
+          <t>614667</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1042164</t>
+          <t>1196978</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1028961</t>
+          <t>1182144</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1052239</t>
+          <t>1208800</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>533932</t>
+          <t>618302</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>533932</t>
+          <t>618302</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533932</t>
+          <t>618302</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1075731</t>
+          <t>1239790</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1075731</t>
+          <t>1239790</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1075731</t>
+          <t>1239790</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>86878</t>
+          <t>96362</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38838</t>
+          <t>78558</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129383</t>
+          <t>118449</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73690</t>
+          <t>73722</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58013</t>
+          <t>62159</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91628</t>
+          <t>87777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>160567</t>
+          <t>170084</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93922</t>
+          <t>147990</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198638</t>
+          <t>194386</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>800908</t>
+          <t>604255</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>758403</t>
+          <t>582168</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>848948</t>
+          <t>622059</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>638004</t>
+          <t>661374</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>620066</t>
+          <t>647319</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>653681</t>
+          <t>672937</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1438913</t>
+          <t>1265629</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1400842</t>
+          <t>1241327</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1505558</t>
+          <t>1287723</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711694</t>
+          <t>735096</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711694</t>
+          <t>735096</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711694</t>
+          <t>735096</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1599480</t>
+          <t>1435713</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1599480</t>
+          <t>1435713</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1599480</t>
+          <t>1435713</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>132761</t>
+          <t>139397</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115947</t>
+          <t>120164</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>154149</t>
+          <t>159702</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>135509</t>
+          <t>151637</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121247</t>
+          <t>134992</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150244</t>
+          <t>169855</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>268270</t>
+          <t>291034</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>245491</t>
+          <t>266807</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>292938</t>
+          <t>319057</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>426514</t>
+          <t>467964</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>405126</t>
+          <t>447659</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>443328</t>
+          <t>487197</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>408600</t>
+          <t>454453</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>393865</t>
+          <t>436235</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>422862</t>
+          <t>471098</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>835114</t>
+          <t>922417</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>810446</t>
+          <t>894394</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>857893</t>
+          <t>946644</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>78,01%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>559275</t>
+          <t>607361</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>559275</t>
+          <t>607361</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>559275</t>
+          <t>607361</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544109</t>
+          <t>606090</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544109</t>
+          <t>606090</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544109</t>
+          <t>606090</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1103384</t>
+          <t>1213451</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1103384</t>
+          <t>1213451</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1103384</t>
+          <t>1213451</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>110601</t>
+          <t>120897</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96048</t>
+          <t>104909</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124447</t>
+          <t>135493</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>346632</t>
+          <t>154635</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>207137</t>
+          <t>140890</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>503280</t>
+          <t>169276</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>457233</t>
+          <t>275532</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>313267</t>
+          <t>255484</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>706859</t>
+          <t>298423</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>254756</t>
+          <t>282939</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>240910</t>
+          <t>268343</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269309</t>
+          <t>298927</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>260597</t>
+          <t>283312</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>103949</t>
+          <t>268671</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>400092</t>
+          <t>297057</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>515353</t>
+          <t>566252</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>265727</t>
+          <t>543361</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>659319</t>
+          <t>586300</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>69,65%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>365357</t>
+          <t>403836</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>365357</t>
+          <t>403836</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>365357</t>
+          <t>403836</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607229</t>
+          <t>437947</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607229</t>
+          <t>437947</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607229</t>
+          <t>437947</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>972586</t>
+          <t>841784</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>972586</t>
+          <t>841784</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>972586</t>
+          <t>841784</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>102408</t>
+          <t>112566</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90492</t>
+          <t>98457</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>116205</t>
+          <t>126302</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>178127</t>
+          <t>192206</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>165001</t>
+          <t>176915</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>191492</t>
+          <t>208297</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>280535</t>
+          <t>304773</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>261821</t>
+          <t>284522</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>300811</t>
+          <t>327170</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,43%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>179487</t>
+          <t>196691</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>165690</t>
+          <t>182955</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>191403</t>
+          <t>210800</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>245194</t>
+          <t>269660</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>231829</t>
+          <t>253569</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>258320</t>
+          <t>284951</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>424680</t>
+          <t>466350</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>404404</t>
+          <t>443953</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>443394</t>
+          <t>486601</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,1%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281895</t>
+          <t>309257</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281895</t>
+          <t>309257</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281895</t>
+          <t>309257</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>423321</t>
+          <t>461866</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>423321</t>
+          <t>461866</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>423321</t>
+          <t>461866</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>705215</t>
+          <t>771123</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>705215</t>
+          <t>771123</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>705215</t>
+          <t>771123</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>464651</t>
+          <t>506606</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>365988</t>
+          <t>468873</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>515380</t>
+          <t>550434</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>756318</t>
+          <t>599485</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>572572</t>
+          <t>564001</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1282956</t>
+          <t>633319</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1220969</t>
+          <t>1106090</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1019748</t>
+          <t>1055483</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1924356</t>
+          <t>1159513</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2987129</t>
+          <t>3017451</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2936400</t>
+          <t>2973623</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3085792</t>
+          <t>3055184</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2896537</t>
+          <t>3126598</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2369899</t>
+          <t>3092764</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3080283</t>
+          <t>3162082</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5883666</t>
+          <t>6144050</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5180279</t>
+          <t>6090627</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6084887</t>
+          <t>6194657</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,44%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3451780</t>
+          <t>3524057</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3451780</t>
+          <t>3524057</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3451780</t>
+          <t>3524057</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3652855</t>
+          <t>3726083</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3652855</t>
+          <t>3726083</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3652855</t>
+          <t>3726083</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7104635</t>
+          <t>7250140</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7104635</t>
+          <t>7250140</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7104635</t>
+          <t>7250140</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
